--- a/data/trans_camb/IP25-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Habitat-trans_camb.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -63,13 +63,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +508,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,21 +523,18 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -564,37 +551,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2012/2007</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>2016/2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>2012/2007</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
         </is>
       </c>
     </row>
@@ -607,9 +579,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,37 +603,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-90,94</t>
+          <t>2,52</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-89,12</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
           <t>0,5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-89,99</t>
         </is>
       </c>
     </row>
@@ -677,47 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 6,89</t>
+          <t>-3,07; 7,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 3,63</t>
+          <t>-7,33; 4,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-94,58; -86,62</t>
+          <t>-3,38; 7,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 8,37</t>
+          <t>-3,11; 8,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 7,55</t>
+          <t>-1,93; 6,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-92,67; -84,49</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-1,81; 5,92</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-3,75; 4,77</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-92,45; -86,52</t>
+          <t>-3,37; 4,84</t>
         </is>
       </c>
     </row>
@@ -740,37 +679,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>0,55%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 7,89</t>
+          <t>-3,34; 8,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 4,11</t>
+          <t>-7,9; 4,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,54; 9,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 9,91</t>
+          <t>-3,43; 9,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 8,64</t>
+          <t>-2,1; 6,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-1,99; 6,72</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 5,43</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-3,71; 5,48</t>
         </is>
       </c>
     </row>
@@ -850,37 +759,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-88,38</t>
+          <t>3,69</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-86,78</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,98</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
           <t>3,25</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-87,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 6,82</t>
+          <t>-1,99; 7,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 7,09</t>
+          <t>-2,51; 6,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-91,44; -84,41</t>
+          <t>-1,28; 8,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 8,77</t>
+          <t>-0,08; 9,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 9,31</t>
+          <t>-0,33; 6,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-90,49; -82,94</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-0,35; 6,67</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,21; 6,62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-89,96; -84,66</t>
+          <t>-0,29; 6,54</t>
         </is>
       </c>
     </row>
@@ -956,37 +835,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
           <t>3,71%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 8,03</t>
+          <t>-2,17; 8,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 8,42</t>
+          <t>-2,77; 8,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,42; 10,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 10,42</t>
+          <t>0,0; 11,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 11,13</t>
+          <t>-0,38; 7,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-0,33; 7,86</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,22; 7,74</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-0,34; 7,7</t>
         </is>
       </c>
     </row>
@@ -1066,37 +915,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-88,75</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,23</t>
+          <t>6,66</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,66</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-88,28</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
           <t>5,64</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-88,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 2,11</t>
+          <t>-10,33; 2,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 9,47</t>
+          <t>-0,38; 10,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-92,63; -83,87</t>
+          <t>-3,52; 7,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 7,8</t>
+          <t>1,44; 11,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 11,48</t>
+          <t>-5,25; 3,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-91,82; -83,13</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-4,63; 3,55</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2,26; 9,33</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-90,94; -85,18</t>
+          <t>2,2; 9,32</t>
         </is>
       </c>
     </row>
@@ -1172,37 +991,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>-1,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-1,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
           <t>6,37%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 2,53</t>
+          <t>-11,47; 2,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 11,11</t>
+          <t>-0,41; 12,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,87; 8,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 9,27</t>
+          <t>1,56; 13,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 13,57</t>
+          <t>-5,76; 3,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-5,16; 4,13</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2,5; 10,85</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>2,4; 10,82</t>
         </is>
       </c>
     </row>
@@ -1282,37 +1071,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-92,74</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,79</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-86,61</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
           <t>-1,98</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>-89,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 0,32</t>
+          <t>-9,33; 0,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,03; -1,15</t>
+          <t>-10,97; -0,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-95,49; -89,08</t>
+          <t>0,96; 11,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 10,52</t>
+          <t>-3,64; 6,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 7,11</t>
+          <t>-2,38; 4,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-90,04; -82,32</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-2,73; 4,4</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-5,75; 1,79</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-91,8; -86,88</t>
+          <t>-5,84; 1,68</t>
         </is>
       </c>
     </row>
@@ -1388,37 +1147,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
           <t>-2,21%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 0,35</t>
+          <t>-9,97; 0,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,67; -1,26</t>
+          <t>-11,74; -1,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,04; 13,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 12,66</t>
+          <t>-4,12; 7,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 8,47</t>
+          <t>-2,61; 4,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-2,96; 5,07</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-6,26; 2,06</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-6,4; 1,88</t>
         </is>
       </c>
     </row>
@@ -1498,37 +1227,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-90,31</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,72</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-87,54</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
           <t>1,71</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>-88,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,47</t>
+          <t>-3,92; 1,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,18</t>
+          <t>-3,33; 1,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-91,9; -88,23</t>
+          <t>1,18; 6,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,59</t>
+          <t>1,33; 6,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,68</t>
+          <t>-0,55; 3,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-89,27; -85,22</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-0,53; 3,18</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-0,16; 3,5</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-90,1; -87,45</t>
+          <t>-0,21; 3,52</t>
         </is>
       </c>
     </row>
@@ -1604,37 +1303,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
           <t>1,93%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,66</t>
+          <t>-4,27; 1,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,46</t>
+          <t>-3,66; 2,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,33; 7,29</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,43; 7,75</t>
+          <t>1,49; 7,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,84</t>
+          <t>-0,62; 3,7</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-0,6; 3,63</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-0,17; 3,98</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-0,27; 3,99</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1370,11 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A19"/>

--- a/data/trans_camb/IP25-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 7,51</t>
+          <t>-3,31; 7,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 4,16</t>
+          <t>-7,17; 4,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 7,94</t>
+          <t>-2,98; 8,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 8,24</t>
+          <t>-3,86; 7,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 6,08</t>
+          <t>-1,66; 6,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 4,84</t>
+          <t>-3,5; 4,83</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 8,61</t>
+          <t>-3,53; 8,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 4,73</t>
+          <t>-7,66; 5,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 9,4</t>
+          <t>-3,26; 9,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 9,53</t>
+          <t>-4,09; 9,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 6,91</t>
+          <t>-1,8; 7,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 5,48</t>
+          <t>-3,83; 5,52</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 7,15</t>
+          <t>-2,48; 6,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,89</t>
+          <t>-2,58; 6,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 8,49</t>
+          <t>-1,83; 8,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 9,19</t>
+          <t>-0,39; 9,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 6,46</t>
+          <t>-0,62; 6,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 6,54</t>
+          <t>-0,13; 6,62</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 8,43</t>
+          <t>-2,7; 7,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 8,22</t>
+          <t>-2,86; 7,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 10,15</t>
+          <t>-2,04; 10,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,02</t>
+          <t>-0,45; 10,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 7,54</t>
+          <t>-0,7; 7,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 7,7</t>
+          <t>-0,15; 7,81</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 2,12</t>
+          <t>-10,18; 2,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 10,29</t>
+          <t>-0,28; 9,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 7,53</t>
+          <t>-3,08; 7,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 11,87</t>
+          <t>1,76; 11,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 3,18</t>
+          <t>-5,52; 2,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,32</t>
+          <t>2,39; 9,3</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 2,31</t>
+          <t>-11,39; 2,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 12,18</t>
+          <t>-0,35; 10,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 8,8</t>
+          <t>-3,31; 8,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 13,98</t>
+          <t>1,99; 13,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 3,7</t>
+          <t>-6,13; 3,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,82</t>
+          <t>2,6; 10,77</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 0,43</t>
+          <t>-8,85; 0,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,97; -0,86</t>
+          <t>-11,01; -0,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 11,09</t>
+          <t>0,77; 10,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 6,65</t>
+          <t>-3,52; 6,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,35</t>
+          <t>-2,56; 4,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 1,68</t>
+          <t>-5,69; 1,14</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 0,44</t>
+          <t>-9,39; 0,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,74; -1,09</t>
+          <t>-11,72; -0,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 13,29</t>
+          <t>0,91; 12,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 7,89</t>
+          <t>-3,89; 8,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,91</t>
+          <t>-2,78; 5,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 1,88</t>
+          <t>-6,29; 1,26</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,42</t>
+          <t>-3,74; 1,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,96</t>
+          <t>-3,02; 2,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,28</t>
+          <t>0,97; 6,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,4</t>
+          <t>1,12; 6,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,26</t>
+          <t>-0,55; 3,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,52</t>
+          <t>0,02; 3,62</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,6</t>
+          <t>-4,13; 1,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,2</t>
+          <t>-3,28; 2,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,29</t>
+          <t>1,13; 7,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,4</t>
+          <t>1,29; 7,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,7</t>
+          <t>-0,61; 3,71</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,99</t>
+          <t>0,01; 4,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP25-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,25</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-1,45</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,52</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 7,22</t>
+          <t>-3,24; 8,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 4,49</t>
+          <t>-3,69; 7,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 8,12</t>
+          <t>-3,72; 6,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 7,8</t>
+          <t>-7,92; 3,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 6,15</t>
+          <t>-1,81; 5,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 4,83</t>
+          <t>-3,75; 4,77</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-1,59%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 8,19</t>
+          <t>-3,48; 9,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 5,22</t>
+          <t>-4,02; 8,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 9,49</t>
+          <t>-4,01; 7,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 9,1</t>
+          <t>-8,33; 4,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 7,1</t>
+          <t>-1,99; 6,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 5,52</t>
+          <t>-4,09; 5,43</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,69</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,47</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1,93</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,69</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 6,79</t>
+          <t>-1,31; 8,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 6,46</t>
+          <t>-0,19; 9,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 8,85</t>
+          <t>-2,19; 6,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 9,25</t>
+          <t>-2,33; 7,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 6,23</t>
+          <t>-0,35; 6,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 6,62</t>
+          <t>0,21; 6,62</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2,49%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2,18%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 7,94</t>
+          <t>-1,46; 10,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 7,73</t>
+          <t>-0,34; 11,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 10,62</t>
+          <t>-2,4; 8,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 10,99</t>
+          <t>-2,54; 8,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 7,27</t>
+          <t>-0,33; 7,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 7,81</t>
+          <t>0,22; 7,74</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,66</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-4,22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>4,55</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,23</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,66</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 2,32</t>
+          <t>-3,03; 7,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 9,32</t>
+          <t>1,85; 11,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 7,41</t>
+          <t>-10,46; 2,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 11,43</t>
+          <t>-0,35; 9,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 2,89</t>
+          <t>-4,63; 3,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 9,3</t>
+          <t>2,26; 9,33</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-4,76%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>5,12%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 2,63</t>
+          <t>-3,29; 9,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 10,86</t>
+          <t>2,06; 13,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 8,77</t>
+          <t>-11,47; 2,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 13,5</t>
+          <t>-0,38; 11,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 3,36</t>
+          <t>-5,16; 4,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,77</t>
+          <t>2,5; 10,85</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,79</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,83</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-4,18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-5,78</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5,79</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 0,28</t>
+          <t>0,33; 10,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,01; -0,81</t>
+          <t>-3,22; 7,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 10,56</t>
+          <t>-9,43; 0,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 6,88</t>
+          <t>-11,03; -1,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 4,44</t>
+          <t>-2,73; 4,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 1,14</t>
+          <t>-5,75; 1,79</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-4,5%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-6,24%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 0,31</t>
+          <t>0,43; 12,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,72; -0,93</t>
+          <t>-3,6; 8,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 12,78</t>
+          <t>-9,98; 0,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 8,17</t>
+          <t>-11,67; -1,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 5,08</t>
+          <t>-2,96; 5,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 1,26</t>
+          <t>-6,26; 2,06</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,72</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,79</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-1,23</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,48</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,79</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,66</t>
+          <t>1,28; 6,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,2</t>
+          <t>1,31; 6,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,22</t>
+          <t>-3,85; 1,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,27</t>
+          <t>-2,99; 2,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,24</t>
+          <t>-0,53; 3,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,62</t>
+          <t>-0,16; 3,5</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-1,36%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-0,54%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,85</t>
+          <t>1,43; 7,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 2,47</t>
+          <t>1,49; 7,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,21</t>
+          <t>-4,22; 1,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,37</t>
+          <t>-3,26; 2,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,71</t>
+          <t>-0,6; 3,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,11</t>
+          <t>-0,17; 3,98</t>
         </is>
       </c>
     </row>
